--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_FCP.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>101.5</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.5</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>12.0</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,11 @@
           <t>diff_casa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q1 (6)</t>
+          <t>Q4 (6)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q3 (1)</t>
+          <t>Q1 (-2)</t>
         </is>
       </c>
     </row>
@@ -675,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,12 +701,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q1 (6)</t>
+          <t>Diff médio casa: 7 | fora: 17</t>
         </is>
       </c>
     </row>
@@ -714,12 +718,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pior período: Q3 (1)</t>
+          <t>Melhor período: Q4 (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pior período: Q1 (-2)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -824,8 +840,41 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>93</v>
+      </c>
+      <c r="E3" t="n">
+        <v>86</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>93</v>
+      </c>
+      <c r="H3" t="n">
+        <v>86</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -924,233 +973,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>25</v>
+        <v>7.5</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>15</v>
+      </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-9</v>
+      </c>
       <c r="E3" t="n">
-        <v>25.9</v>
+        <v>21.4</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>-2</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>21</v>
+      </c>
       <c r="E4" t="n">
-        <v>27.1</v>
+        <v>16.4</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-2</v>
+      </c>
       <c r="E5" t="n">
-        <v>23.6</v>
+        <v>25.2</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-13</v>
+      </c>
       <c r="E6" t="n">
-        <v>25.2</v>
+        <v>23.6</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>-4.5</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>-3</v>
+      </c>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
       <c r="E7" t="n">
-        <v>19.4</v>
+        <v>28</v>
       </c>
       <c r="F7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" t="n">
         <v>11</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>-8</v>
+      </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. Williams</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
       <c r="E8" t="n">
-        <v>21.4</v>
+        <v>27.1</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>-9</v>
+      </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>V. Voytso</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14</v>
+      </c>
       <c r="E9" t="n">
-        <v>16.4</v>
+        <v>25.9</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>-15</v>
+      </c>
       <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1260,25 +1373,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="3">
@@ -1303,22 +1416,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -1346,25 +1459,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>29</v>
+        <v>30.5</v>
       </c>
       <c r="J4" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1502,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1541,46 +1654,46 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -1589,40 +1702,48 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
       <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
@@ -1630,62 +1751,62 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -1698,7 +1819,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -1707,13 +1828,13 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -1722,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1731,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1746,149 +1867,155 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1896,9 +2023,11 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1906,37 +2035,45 @@
           <t>G. Delgado</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
       <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -1959,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2037,8 +2174,37 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922726</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>86</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_FCP.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>97.8</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>8.8</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>10.5</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q4 (6)</t>
+          <t>Q2 (5)</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 7 | fora: 17</t>
+          <t>Diff médio casa: 7 | fora: 10.5</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q4 (6)</t>
+          <t>Melhor período: Q2 (5)</t>
         </is>
       </c>
     </row>
@@ -819,25 +819,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>110</v>
+        <v>205</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>102.5</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="3">
@@ -986,24 +986,24 @@
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -1023,61 +1023,61 @@
         <v>-9</v>
       </c>
       <c r="E3" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-2</v>
+        <v>0.3</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>33.4</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>16.4</v>
+        <v>27.4</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>17.7</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
@@ -1097,98 +1097,98 @@
         <v>-2</v>
       </c>
       <c r="E5" t="n">
-        <v>25.2</v>
+        <v>27.6</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>-1.5</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.1</v>
+        <v>7.7</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-13</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>23.6</v>
+        <v>14.8</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="H6" t="n">
-        <v>10.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.4</v>
+        <v>19.1</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>-13</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>23.4</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>13.5</v>
       </c>
       <c r="G7" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>-2.7</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-8</v>
+        <v>-4.5</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
@@ -1208,24 +1208,24 @@
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>27.1</v>
+        <v>23.7</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-9</v>
+        <v>-4.5</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -1245,24 +1245,24 @@
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>25.9</v>
+        <v>23.4</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="I9" t="n">
-        <v>14.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H2" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>22.3</v>
       </c>
       <c r="J2" t="n">
-        <v>23</v>
+        <v>24.3</v>
       </c>
       <c r="K2" t="n">
         <v>-2</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>25.3</v>
       </c>
       <c r="J3" t="n">
-        <v>21</v>
+        <v>20.3</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -1459,25 +1459,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>30.5</v>
+        <v>27.7</v>
       </c>
       <c r="J4" t="n">
-        <v>27.5</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="5">
@@ -1502,25 +1502,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="G5" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>18</v>
+        <v>22.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
     </row>
   </sheetData>
@@ -1651,159 +1651,159 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="C4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
-        <v>7</v>
-      </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5</v>
-      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
         <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
@@ -1812,56 +1812,56 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2.5</v>
       </c>
-      <c r="H5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
       <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.5</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -1871,37 +1871,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -1929,19 +1929,19 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1950,56 +1950,56 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>A. Bessa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
         <v>2.5</v>
       </c>
-      <c r="D8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.5</v>
@@ -2008,80 +2008,80 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. Delgado</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.5</v>
-      </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2096,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2203,8 +2203,37 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922731</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>95</v>
+      </c>
+      <c r="F4" t="n">
+        <v>91</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_FCP.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>9.8</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (5)</t>
+          <t>Q2 (4.2)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q1 (-2)</t>
+          <t>Q1 (1.2)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 7 | fora: 10.5</t>
+          <t>Diff médio casa: 9 | fora: 10.5</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (5)</t>
+          <t>Melhor período: Q2 (4.2)</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pior período: Q1 (-2)</t>
+          <t>Pior período: Q1 (1.2)</t>
         </is>
       </c>
     </row>
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>186</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
         <v>93</v>
       </c>
       <c r="H3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -973,296 +973,296 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.3</v>
+        <v>22.2</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="H2" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>11.5</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="D3" t="n">
-        <v>-9</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>21.2</v>
+        <v>13.1</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
-        <v>9.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33.4</v>
+        <v>18.8</v>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H4" t="n">
-        <v>17.7</v>
+        <v>8.5</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.5</v>
+        <v>19.5</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="D5" t="n">
-        <v>-2</v>
+        <v>7.5</v>
       </c>
       <c r="E5" t="n">
-        <v>27.6</v>
+        <v>23.4</v>
       </c>
       <c r="F5" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>10.3</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-1.5</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>C. Dundao</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.7</v>
+        <v>20.9</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8</v>
+        <v>23.7</v>
       </c>
       <c r="F6" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.1</v>
+        <v>26.1</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="E7" t="n">
-        <v>23.4</v>
+        <v>27.6</v>
       </c>
       <c r="F7" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>16.5</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.7</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-4.5</v>
+        <v>-5.5</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.4</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>-0.5</v>
       </c>
       <c r="E8" t="n">
-        <v>23.7</v>
+        <v>27.4</v>
       </c>
       <c r="F8" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-4.5</v>
+        <v>-8</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>-6.5</v>
       </c>
       <c r="E9" t="n">
         <v>23.4</v>
       </c>
       <c r="F9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H9" t="n">
         <v>9</v>
       </c>
-      <c r="G9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.3</v>
-      </c>
       <c r="I9" t="n">
-        <v>9.300000000000001</v>
+        <v>-2</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="G2" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="H2" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
       <c r="J2" t="n">
-        <v>24.3</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>-2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="3">
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="G3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>25.3</v>
+        <v>24.5</v>
       </c>
       <c r="J3" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4">
@@ -1459,25 +1459,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -1502,25 +1502,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="J5" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1651,52 +1651,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -1706,40 +1706,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M3" t="n">
         <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
@@ -1748,10 +1748,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -1812,47 +1812,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Woodard</t>
+          <t>G. Delgado</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1861,59 +1861,59 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. Williams</t>
+          <t>J. Woodard</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D6" t="n">
         <v>2.3</v>
       </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
       <c r="E6" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="F6" t="n">
         <v>1.3</v>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.3</v>
@@ -1926,22 +1926,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1950,138 +1950,138 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. Bessa</t>
+          <t>V. Voytso</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7</v>
+        <v>0.2</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" t="n">
         <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5</v>
       </c>
       <c r="M8" t="n">
         <v>0.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. Voytso</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="E9" t="n">
         <v>2.7</v>
       </c>
       <c r="F9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.3</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0.3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2096,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2232,8 +2232,37 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2922737</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>93</v>
+      </c>
+      <c r="F5" t="n">
+        <v>82</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>